--- a/data/trans_dic/IP16B02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16B02-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre (tasa de respuesta: 98,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,1; 100,0</t>
+          <t>29,3; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,93; 93,27</t>
+          <t>47,67; 93,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,74; 100,0</t>
+          <t>47,72; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70,31; 100,0</t>
+          <t>68,42; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,72; 100,0</t>
+          <t>40,47; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,5; 91,04</t>
+          <t>36,09; 90,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,4; 97,34</t>
+          <t>72,43; 97,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57,22; 91,77</t>
+          <t>56,86; 91,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,17; 93,48</t>
+          <t>53,67; 93,43</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,49; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,29; 100,0</t>
+          <t>57,03; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,18; 93,34</t>
+          <t>39,39; 93,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,99; 100,0</t>
+          <t>60,23; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,9; 96,5</t>
+          <t>67,11; 96,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,55; 96,76</t>
+          <t>67,26; 96,85</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,96; 85,78</t>
+          <t>11,94; 85,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,83; 100,0</t>
+          <t>59,48; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46,08; 100,0</t>
+          <t>42,6; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,39; 93,01</t>
+          <t>40,49; 92,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,16; 100,0</t>
+          <t>63,22; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,22; 84,42</t>
+          <t>38,43; 83,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,98; 96,61</t>
+          <t>68,75; 96,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74,63; 100,0</t>
+          <t>64,27; 100,0</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,41; 94,76</t>
+          <t>57,42; 94,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,07; 97,18</t>
+          <t>74,88; 97,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,81; 100,0</t>
+          <t>81,7; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65,88; 96,02</t>
+          <t>68,61; 96,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,94; 94,86</t>
+          <t>70,22; 94,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,61; 95,83</t>
+          <t>62,92; 96,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,94; 93,14</t>
+          <t>69,13; 91,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76,98; 93,85</t>
+          <t>77,16; 94,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79,38; 96,52</t>
+          <t>79,94; 96,64</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,53; 100,0</t>
+          <t>52,99; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,75; 85,31</t>
+          <t>49,87; 85,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,34; 86,57</t>
+          <t>43,94; 85,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66,34; 100,0</t>
+          <t>63,38; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>77,41; 100,0</t>
+          <t>77,43; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,34; 100,0</t>
+          <t>73,24; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>69,29; 91,67</t>
+          <t>68,56; 90,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64,59; 90,85</t>
+          <t>64,31; 91,43</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,6; 100,0</t>
+          <t>46,09; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,21; 100,0</t>
+          <t>31,91; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>81,26; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63,4; 100,0</t>
+          <t>62,92; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,63; 100,0</t>
+          <t>63,15; 100,0</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,84; 91,17</t>
+          <t>72,28; 91,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,03; 88,22</t>
+          <t>73,94; 88,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75,13; 91,14</t>
+          <t>74,49; 90,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,94; 94,6</t>
+          <t>81,23; 95,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,97; 94,2</t>
+          <t>81,27; 94,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,93; 95,26</t>
+          <t>80,88; 95,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,29; 92,34</t>
+          <t>80,03; 91,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79,9; 89,34</t>
+          <t>79,72; 89,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80,15; 90,94</t>
+          <t>80,85; 91,37</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre (tasa de respuesta: 98,35%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3566</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7655</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4645</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11327</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5869</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14893</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>13525</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9043</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1410; 4811</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4700; 9215</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2564; 5374</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8246; 12052</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3064; 7570</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2292; 5762</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12214; 16405</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9912; 16017</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6292; 10953</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7824</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9371</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6075</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7383</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6295</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9519</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15208</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15667</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>15594</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6108; 10709</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3204; 7595</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4185; 6949</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>11851; 17042</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>11873; 17096</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7209</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4331</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4846</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9963</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7333</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>17172</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10247</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>559; 3997</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5068; 8521</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2112; 4957</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2696; 6178</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7146; 11304</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4357; 9510</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13629; 19084</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6988; 10873</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9711</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20577</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21644</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14715</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22447</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11137</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24425</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>43025</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>32781</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6799; 11230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17366; 22540</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18844; 23066</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11936; 16732</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>18353; 24679</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8292; 12661</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>20213; 26700</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>38061; 46457</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>28974; 35024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5158</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12023</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9665</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8577</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14495</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9717</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13735</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>26518</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>19382</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3050; 5755</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8656; 14764</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6336; 12346</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5867; 9257</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11745; 15168</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10995; 15012</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>22297; 29406</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>15523; 22068</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2606</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6846</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3307</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3556</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>11044</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>6657</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3871; 8399</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1343; 4208</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>7926; 12597</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>4616; 7309</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>31353</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>63680</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>49462</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>50154</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>63269</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>44243</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>81508</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>126950</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>93703</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>27117; 34394</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>57699; 68691</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>43986; 53514</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>45532; 53367</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>57965; 67163</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>39540; 46745</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>74887; 85961</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>119079; 133101</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>87262; 98620</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16B02-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,3; 100,0</t>
+          <t>32,06; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,67; 93,46</t>
+          <t>48,05; 93,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,72; 100,0</t>
+          <t>47,21; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68,42; 100,0</t>
+          <t>70,27; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,47; 100,0</t>
+          <t>42,55; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,09; 90,75</t>
+          <t>29,89; 90,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,43; 97,28</t>
+          <t>70,09; 97,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,86; 91,89</t>
+          <t>56,92; 91,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,67; 93,43</t>
+          <t>53,27; 93,87</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,03; 100,0</t>
+          <t>61,02; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,39; 93,37</t>
+          <t>35,57; 93,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,23; 100,0</t>
+          <t>59,38; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>67,11; 96,5</t>
+          <t>70,02; 96,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67,26; 96,85</t>
+          <t>66,75; 96,76</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,94; 85,41</t>
+          <t>13,69; 85,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,48; 100,0</t>
+          <t>53,43; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,6; 100,0</t>
+          <t>40,83; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40,49; 92,81</t>
+          <t>34,36; 92,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,22; 100,0</t>
+          <t>59,98; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,43; 83,88</t>
+          <t>40,54; 87,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>68,75; 96,26</t>
+          <t>69,34; 96,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64,27; 100,0</t>
+          <t>75,2; 100,0</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,42; 94,83</t>
+          <t>58,16; 94,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,88; 97,19</t>
+          <t>73,42; 97,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,7; 100,0</t>
+          <t>82,08; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68,61; 96,18</t>
+          <t>65,62; 96,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,22; 94,42</t>
+          <t>71,35; 94,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,92; 96,09</t>
+          <t>61,29; 95,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,13; 91,32</t>
+          <t>69,48; 92,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>77,16; 94,18</t>
+          <t>76,72; 93,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79,94; 96,64</t>
+          <t>79,63; 96,27</t>
         </is>
       </c>
     </row>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,99; 100,0</t>
+          <t>54,95; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,87; 85,06</t>
+          <t>48,82; 85,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,94; 85,62</t>
+          <t>44,11; 84,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,38; 100,0</t>
+          <t>69,94; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>77,43; 100,0</t>
+          <t>81,98; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,24; 100,0</t>
+          <t>73,53; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,56; 90,41</t>
+          <t>68,89; 91,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64,31; 91,43</t>
+          <t>63,42; 91,47</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,09; 100,0</t>
+          <t>49,71; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,91; 100,0</t>
+          <t>34,98; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>62,92; 100,0</t>
+          <t>65,01; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63,15; 100,0</t>
+          <t>63,49; 100,0</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,28; 91,67</t>
+          <t>72,68; 91,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,94; 88,03</t>
+          <t>73,62; 87,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,49; 90,62</t>
+          <t>75,67; 90,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81,23; 95,21</t>
+          <t>81,35; 95,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,27; 94,16</t>
+          <t>81,34; 93,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,88; 95,62</t>
+          <t>80,67; 95,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,03; 91,87</t>
+          <t>81,1; 91,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79,72; 89,11</t>
+          <t>79,38; 89,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80,85; 91,37</t>
+          <t>80,7; 91,64</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1410; 4811</t>
+          <t>1542; 4811</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4700; 9215</t>
+          <t>4737; 9189</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2564; 5374</t>
+          <t>2537; 5374</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8246; 12052</t>
+          <t>8469; 12052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3064; 7570</t>
+          <t>3221; 7570</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2292; 5762</t>
+          <t>1898; 5762</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12214; 16405</t>
+          <t>11819; 16415</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9912; 16017</t>
+          <t>9922; 15923</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6292; 10953</t>
+          <t>6245; 11004</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6108; 10709</t>
+          <t>6535; 10709</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3204; 7595</t>
+          <t>2894; 7587</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4185; 6949</t>
+          <t>4126; 6949</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11851; 17042</t>
+          <t>12365; 17030</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11873; 17096</t>
+          <t>11784; 17082</t>
         </is>
       </c>
     </row>
@@ -1965,27 +1965,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>559; 3997</t>
+          <t>641; 4016</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5068; 8521</t>
+          <t>4553; 8521</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2112; 4957</t>
+          <t>2024; 4957</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2696; 6178</t>
+          <t>2288; 6176</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7146; 11304</t>
+          <t>6780; 11304</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4357; 9510</t>
+          <t>4596; 9930</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13629; 19084</t>
+          <t>13746; 19149</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6988; 10873</t>
+          <t>8176; 10873</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6799; 11230</t>
+          <t>6887; 11220</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17366; 22540</t>
+          <t>17027; 22545</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18844; 23066</t>
+          <t>18934; 23066</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11936; 16732</t>
+          <t>11416; 16718</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18353; 24679</t>
+          <t>18648; 24788</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8292; 12661</t>
+          <t>8076; 12614</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20213; 26700</t>
+          <t>20314; 27094</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38061; 46457</t>
+          <t>37847; 46208</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28974; 35024</t>
+          <t>28859; 34890</t>
         </is>
       </c>
     </row>
@@ -2291,27 +2291,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3050; 5755</t>
+          <t>3163; 5755</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8656; 14764</t>
+          <t>8474; 14788</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6336; 12346</t>
+          <t>6360; 12215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5867; 9257</t>
+          <t>6474; 9257</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11745; 15168</t>
+          <t>12435; 15168</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10995; 15012</t>
+          <t>11038; 15012</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22297; 29406</t>
+          <t>22405; 29770</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15523; 22068</t>
+          <t>15308; 22077</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3871; 8399</t>
+          <t>4175; 8399</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1343; 4208</t>
+          <t>1472; 4208</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7926; 12597</t>
+          <t>8189; 12597</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4616; 7309</t>
+          <t>4640; 7309</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>27117; 34394</t>
+          <t>27268; 34471</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>57699; 68691</t>
+          <t>57448; 68653</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43986; 53514</t>
+          <t>44682; 53573</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45532; 53367</t>
+          <t>45600; 53335</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>57965; 67163</t>
+          <t>58014; 66945</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39540; 46745</t>
+          <t>39439; 46833</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74887; 85961</t>
+          <t>75890; 85892</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>119079; 133101</t>
+          <t>118563; 133257</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>87262; 98620</t>
+          <t>87110; 98914</t>
         </is>
       </c>
     </row>
